--- a/resampling/input/accessibility_reports_generated/IRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/IRC_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O84" headerRowCount="1">
-  <autoFilter ref="A1:O84"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P97" headerRowCount="1">
+  <autoFilter ref="A1:P97"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 144 wards, 83 clusters</t>
+          <t>Assigned to you: 144 wards, 96 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -853,13 +864,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -905,10 +916,10 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -931,7 +942,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shinkafi 2</t>
+          <t>Dandagoro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -942,7 +953,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaita; Katsina</t>
+          <t>Katsina; Rimi</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -954,10 +965,10 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -980,7 +991,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kayauki</t>
+          <t>Shinkafi 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -991,7 +1002,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaita; Katsina; Rimi</t>
+          <t>Kaita; Katsina</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1000,13 +1011,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1029,7 +1040,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dabaibayawa</t>
+          <t>Barawa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1040,7 +1051,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1049,13 +1060,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1078,7 +1089,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dandagoro</t>
+          <t>Tsanni</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1089,7 +1100,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Katsina; Rimi</t>
+          <t>Kurfi; Rimi</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1098,13 +1109,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1127,7 +1138,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Barawa</t>
+          <t>Kayauki</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1138,7 +1149,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Kaita; Katsina; Rimi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1147,13 +1158,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1176,7 +1187,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tsanni</t>
+          <t>Dabaibayawa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1187,7 +1198,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kurfi; Rimi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1196,13 +1207,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1934,10 +1945,10 @@
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -3006,17 +3017,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dabai</t>
+          <t>Senchi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fakai</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>4</v>
       </c>
@@ -3024,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -3047,33 +3066,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manga Ushe</t>
+          <t>Dabai</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Fakai</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3096,25 +3107,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rikoto</t>
+          <t>Manga Ushe</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fakai</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3137,25 +3156,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Senchi</t>
+          <t>Rikoto</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Fakai</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -3337,7 +3348,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -5463,13 +5474,13 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J100" t="n">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
@@ -5492,7 +5503,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kalanjeni</t>
+          <t>Salewa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -5503,7 +5514,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kware</t>
+          <t>Gwadabawa; Illela</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5518,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
@@ -5541,7 +5552,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Magonho</t>
+          <t>Gidan Madi</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -5552,7 +5563,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gudu</t>
+          <t>Binji</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5561,13 +5572,13 @@
         </is>
       </c>
       <c r="H102" t="n">
+        <v>3</v>
+      </c>
+      <c r="I102" t="n">
         <v>2</v>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
       <c r="J102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
@@ -5590,7 +5601,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gidan Madi</t>
+          <t>Jamali</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -5601,7 +5612,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Binji</t>
+          <t>Binji; Gudu</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5610,13 +5621,13 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
@@ -5639,7 +5650,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamali</t>
+          <t>Atakwanyo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -5650,7 +5661,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Binji; Gudu</t>
+          <t>Gwadabawa; Kware</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5659,13 +5670,13 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -5688,7 +5699,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Salewa</t>
+          <t>Balle</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -5699,7 +5710,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gwadabawa; Illela</t>
+          <t>Gudu</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -5708,13 +5719,13 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
@@ -5737,7 +5748,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sutti</t>
+          <t>Damba</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -5748,7 +5759,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Binji; Gwadabawa</t>
+          <t>Gwadabawa; Illela</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5757,13 +5768,13 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
@@ -5786,7 +5797,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atakwanyo</t>
+          <t>Gidan Hamidu</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -5797,7 +5808,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gwadabawa; Kware</t>
+          <t>Kware; Wamako</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5835,7 +5846,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Balle</t>
+          <t>Gigane</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -5846,7 +5857,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gudu</t>
+          <t>Gwadabawa; Illela</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5884,7 +5895,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Damba</t>
+          <t>Inname</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -5895,7 +5906,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gwadabawa; Illela</t>
+          <t>Binji</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5933,7 +5944,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gidan Hamidu</t>
+          <t>Kalanjeni</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -5944,7 +5955,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kware; Wamako</t>
+          <t>Kware</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5982,7 +5993,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gigane</t>
+          <t>Kalmalo</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -5993,7 +6004,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gwadabawa; Illela</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6031,7 +6042,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inname</t>
+          <t>Kaura</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -6042,7 +6053,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Binji</t>
+          <t>Wamako</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6080,7 +6091,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kalmalo</t>
+          <t>Kwacce Huru</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -6091,7 +6102,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Illela</t>
+          <t>Binji; Kware; Wamako</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6129,7 +6140,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kaura</t>
+          <t>Magonho</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -6140,7 +6151,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wamako</t>
+          <t>Gudu</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6178,7 +6189,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kwacce Huru</t>
+          <t>Marake</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -6189,7 +6200,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Binji; Kware; Wamako</t>
+          <t>Gudu</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6227,7 +6238,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Marake</t>
+          <t>Raka</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -6238,7 +6249,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gudu</t>
+          <t>Gwadabawa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6276,7 +6287,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Raka</t>
+          <t>Ruwa Wuri</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -6287,7 +6298,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Gudu; Illela</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6325,7 +6336,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ruwa Wuri</t>
+          <t>Sabon Birni</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -6336,7 +6347,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gudu; Illela</t>
+          <t>Gwadabawa; Kebbe; Kware; Sabon Birni; Tambuwal</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6374,7 +6385,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sabon Birni</t>
+          <t>Sakkwai</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -6385,7 +6396,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gwadabawa; Kebbe; Kware; Sabon Birni; Tambuwal</t>
+          <t>Gudu</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6423,7 +6434,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sakkwai</t>
+          <t>Samama</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -6434,7 +6445,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gudu</t>
+          <t>Binji; Wamako</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6472,7 +6483,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Samama</t>
+          <t>Sutti</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -6483,7 +6494,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Binji; Wamako</t>
+          <t>Binji; Gwadabawa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7628,7 +7639,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7644,7 +7655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7652,16 +7663,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7692,50 +7704,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -7769,26 +7786,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7818,26 +7840,31 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7867,26 +7894,31 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7916,26 +7948,31 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7965,26 +8002,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8014,26 +8056,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8063,26 +8110,31 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8097,23 +8149,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dandagoro</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_12</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>idp_NG021002_supp1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8121,13 +8177,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8142,23 +8203,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kayauki</t>
+          <t>Dandagoro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_13</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>idp_NG021002_supp2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8166,13 +8231,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8187,23 +8257,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kayauki</t>
+          <t>Dandagoro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_14</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>idp_NG021002_supp3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8211,13 +8285,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8232,23 +8311,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ajiwa</t>
+          <t>Dandagoro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_15</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>idp_NG021002_supp4</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8256,13 +8339,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8277,7 +8365,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Barawa</t>
+          <t>Dandagoro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8287,27 +8375,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_17</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8322,7 +8415,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jino</t>
+          <t>Kayauki</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8332,27 +8425,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_2</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_13</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8367,7 +8465,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dabaibayawa</t>
+          <t>Kayauki</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8377,27 +8475,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_3</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_14</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8412,7 +8515,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dabaibayawa</t>
+          <t>Ajiwa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8422,27 +8525,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_4</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_15</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8457,7 +8565,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dandagoro</t>
+          <t>Barawa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -8467,27 +8575,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_5</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_17</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8502,7 +8615,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shinkafi 2</t>
+          <t>Jino</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8512,27 +8625,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_7</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8547,7 +8665,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ajiwa</t>
+          <t>Dabaibayawa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8557,27 +8675,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_8</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8592,7 +8715,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tsanni</t>
+          <t>Dabaibayawa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8602,27 +8725,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG021002_supp1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8632,46 +8760,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kusa</t>
+          <t>Dandagoro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>idp_NG021016_5</t>
+          <t>non_idp_NG021002_5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8681,46 +8810,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kusa</t>
+          <t>Shinkafi 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>idp_NG021016_7</t>
+          <t>non_idp_NG021002_7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8730,46 +8860,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kusa</t>
+          <t>Ajiwa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>idp_NG021016_supp1</t>
+          <t>non_idp_NG021002_8</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8779,12 +8910,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bugaje</t>
+          <t>Tsanni</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8794,27 +8925,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_10</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_supp1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8824,12 +8960,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kusa</t>
+          <t>Ajiwa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8839,27 +8975,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_11</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_supp2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8869,12 +9010,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bugaje</t>
+          <t>Tsanni</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8884,27 +9025,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_13</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_supp3</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8914,12 +9060,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jibia</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kusa</t>
+          <t>Barawa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8929,27 +9075,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_14</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021002_supp4</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8964,37 +9115,46 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bugaje</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_15</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>idp_NG021016_5</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9009,37 +9169,46 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faru</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_2</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>idp_NG021016_7</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9054,23 +9223,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bugaje</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_8</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>idp_NG021016_supp1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9078,13 +9251,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9104,32 +9282,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_9</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>idp_NG021016_supp2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9144,7 +9331,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kusa</t>
+          <t>Bugaje</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9154,27 +9341,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9189,7 +9381,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bugaje</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9199,27 +9391,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp2</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_11</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9234,7 +9431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Darini Magaji Abu</t>
+          <t>Bugaje</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9244,27 +9441,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp3</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_13</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9279,7 +9481,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bugaje</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -9289,27 +9491,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp4</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_14</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9334,27 +9541,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp5</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_15</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9369,7 +9581,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arewa 2</t>
+          <t>Faru</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -9379,27 +9591,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp6</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_2</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9414,7 +9631,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kusa</t>
+          <t>Bugaje</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -9424,27 +9641,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp7</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_8</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9459,7 +9681,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Darini Magaji Abu</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -9469,42 +9691,47 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG021016_supp8</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_9</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dabai</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -9514,42 +9741,47 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_11</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dabai</t>
+          <t>Bugaje</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -9559,42 +9791,47 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_12</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bedi</t>
+          <t>Darini Magaji Abu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -9604,42 +9841,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_13</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp3</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bedi</t>
+          <t>Bugaje</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9649,42 +9891,47 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_15</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp4</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Senchi</t>
+          <t>Bugaje</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9694,42 +9941,47 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_2</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp5</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dabai</t>
+          <t>Arewa 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9739,42 +9991,47 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_3</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp6</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Manga Ushe</t>
+          <t>Kusa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9784,42 +10041,47 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_4</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp7</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zuru</t>
+          <t>Jibia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rikoto</t>
+          <t>Darini Magaji Abu</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9829,27 +10091,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_5</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG021016_supp8</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9864,7 +10131,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedi</t>
+          <t>Dabai</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9874,27 +10141,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_8</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_11</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9909,7 +10181,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bedi</t>
+          <t>Dabai</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -9919,27 +10191,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_supp1</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_12</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9954,7 +10231,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manga Ushe</t>
+          <t>Bedi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -9964,27 +10241,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_supp2</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_13</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10009,238 +10291,247 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>non_idp_NG022021_supp3</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Senchi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>idp_NG034019_1</t>
+          <t>non_idp_NG022021_2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gidan Madi</t>
+          <t>Dabai</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>idp_NG034019_16</t>
+          <t>non_idp_NG022021_3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gidan Madi</t>
+          <t>Manga Ushe</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>idp_NG034019_5</t>
+          <t>non_idp_NG022021_4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Rikoto</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>idp_NG034019_6</t>
+          <t>non_idp_NG022021_5</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Bedi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -10250,42 +10541,47 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_10</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_8</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Bedi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -10295,42 +10591,47 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_12</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_supp1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gidan Madi</t>
+          <t>Manga Ushe</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10340,42 +10641,47 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_14</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_supp2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sutti</t>
+          <t>Bedi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -10385,42 +10691,47 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_15</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_supp3</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kalanjeni</t>
+          <t>Senchi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10430,42 +10741,47 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_16</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_supp4</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Zuru</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kalanjeni</t>
+          <t>Senchi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10475,27 +10791,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_2</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG022021_supp5</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10510,37 +10831,46 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Magonho</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_7</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>idp_NG034019_1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10555,37 +10885,46 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Gidan Madi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_9</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>idp_NG034019_16</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10600,23 +10939,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tangaza</t>
+          <t>Gidan Madi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_supp1</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>idp_NG034019_5</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10624,13 +10967,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10645,37 +10993,46 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Magonho</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_supp2</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>idp_NG034019_6</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10695,32 +11052,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_supp3</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>idp_NG034019_supp1</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10735,37 +11101,46 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jamali</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_supp4</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>idp_NG034019_supp2</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10780,37 +11155,46 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salewa</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_supp5</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>idp_NG034019_supp3</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10825,37 +11209,46 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gidan Madi</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_supp6</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>idp_NG034019_supp4</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10875,47 +11268,56 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>non_idp_NG034019_supp7</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>idp_NG034019_supp5</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" s="10" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tsafe Central</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10925,42 +11327,47 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_11</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_12</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tsafe Central</t>
+          <t>Gidan Madi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10970,42 +11377,47 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp1</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_14</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" s="10" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tsafe Central</t>
+          <t>Gidan Madi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11015,42 +11427,47 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp10</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_15</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tsafe Central</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -11060,42 +11477,47 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp11</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_9</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" s="10" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Keta</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -11105,42 +11527,47 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp12</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Keta</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11150,42 +11577,47 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp13</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp10</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" s="10" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mada</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11195,42 +11627,47 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp16</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp3</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tsafe Central</t>
+          <t>Jamali</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11240,42 +11677,47 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp17</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp4</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" s="10" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Keta</t>
+          <t>Salewa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11285,42 +11727,47 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp18</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp5</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Keta</t>
+          <t>Gidan Madi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11330,42 +11777,47 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp3</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp6</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" s="10" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tsafe Central</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11375,42 +11827,47 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp4</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp7</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" s="10" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Yankuzo B</t>
+          <t>Salewa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11420,42 +11877,47 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp5</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp8</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" s="10" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Keta</t>
+          <t>Tangaza</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11465,27 +11927,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp6</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034019_supp9</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" s="10" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11510,45 +11977,700 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>non_idp_NG037013_supp7</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037013_11</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" s="10" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp10</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp11</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp12</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Mada</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp16</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp17</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp18</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp3</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp4</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Yankuzo B</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp5</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp6</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp7</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11814,13 +12936,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EFEDBAF-F58C-405C-8AF3-F942505DB959}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6050C92-E0EF-46D4-A8F5-819BC8720BC1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5768927-6339-403B-84FD-D3974848EA16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9AE9117-69BA-422B-8613-5F6128FD6CF4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{183B805D-30BF-45EC-9442-E468BF70B42C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{933314E0-F14E-4FA2-A857-C1D17C24A3B6}"/>
 </file>